--- a/Result/profitability/6641.xlsx
+++ b/Result/profitability/6641.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5260,6 +5260,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6641</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>563</v>
+      </c>
+      <c r="D39" t="n">
+        <v>384</v>
+      </c>
+      <c r="E39" t="n">
+        <v>179</v>
+      </c>
+      <c r="F39" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.11125</v>
+      </c>
+      <c r="N39" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.8200000000000003</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.02652863151083795</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-2.0625</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-0.4400000000000013</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.0136773391358409</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
